--- a/final_project/SM Competitions 11-7-2025.xlsx
+++ b/final_project/SM Competitions 11-7-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mallo/Documents/Projects/biol696/collins_mallory_biol696_workflows/final_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD45ED6A-A6FB-344C-9DA0-8D413F066A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1376D64E-6840-B24D-8856-5AD744939DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15920" activeTab="1" xr2:uid="{F461D164-D39E-5F43-8C81-7877C5AB1617}"/>
   </bookViews>
